--- a/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U70_P03S49_RelayUserCount_OnlyBPLR_vs_SAPR-R.xlsx
+++ b/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U70_P03S49_RelayUserCount_OnlyBPLR_vs_SAPR-R.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="68" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="102" uniqueCount="7">
   <si>
     <t>time_offset_from_worst_epfd_slot_s</t>
   </si>
@@ -28,6 +28,12 @@
   </si>
   <si>
     <t>relay_user_count</t>
+  </si>
+  <si>
+    <t>Only HBR</t>
+  </si>
+  <si>
+    <t>EABR</t>
   </si>
 </sst>
 </file>
@@ -76,9 +82,9 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" customWidth="true"/>
-    <col min="2" max="2" width="9.21875" customWidth="true"/>
-    <col min="3" max="3" width="15.109375" customWidth="true"/>
+    <col min="1" max="1" width="34.140625" customWidth="true"/>
+    <col min="2" max="2" width="9.28515625" customWidth="true"/>
+    <col min="3" max="3" width="16.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -97,7 +103,7 @@
         <v>-60</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2" s="0">
         <v>0</v>
@@ -108,7 +114,7 @@
         <v>-40</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" s="0">
         <v>6.3571428571428568</v>
@@ -119,7 +125,7 @@
         <v>-20</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" s="0">
         <v>8.0999999999999996</v>
@@ -130,7 +136,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5" s="0">
         <v>9.3333333333333339</v>
@@ -141,7 +147,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6" s="0">
         <v>8.9499999999999993</v>
@@ -152,7 +158,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" s="0">
         <v>6.4375</v>
@@ -163,7 +169,7 @@
         <v>60</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" s="0">
         <v>0</v>
@@ -174,7 +180,7 @@
         <v>-60</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C9" s="0">
         <v>0</v>
@@ -185,7 +191,7 @@
         <v>-40</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10" s="0">
         <v>10.142857142857142</v>
@@ -196,7 +202,7 @@
         <v>-20</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C11" s="0">
         <v>23.25</v>
@@ -207,7 +213,7 @@
         <v>0</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C12" s="0">
         <v>27.904761904761905</v>
@@ -218,7 +224,7 @@
         <v>20</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C13" s="0">
         <v>22.850000000000001</v>
@@ -229,7 +235,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C14" s="0">
         <v>10.1875</v>
@@ -240,7 +246,7 @@
         <v>60</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C15" s="0">
         <v>0</v>
